--- a/Compititor's_Price/IKO_Prices/IKO_Prices_29-09-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_29-09-2025.xlsx
@@ -555,17 +555,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.59</t>
+          <t>£12.57</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.59</t>
+          <t>£12.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.59</t>
+          <t>£12.57</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -612,17 +612,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.12</t>
+          <t>£16.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.12</t>
+          <t>£16.07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£16.12</t>
+          <t>£16.07</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£22.84</t>
+          <t>£22.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£22.84</t>
+          <t>£22.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£22.84</t>
+          <t>£22.79</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>£23.05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>£23.10</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>£23.10</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£23.10</t>
+          <t>£23.05</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>£26.44</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>£26.46</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>£26.46</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.46</t>
+          <t>£26.44</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£28.67</t>
+          <t>£28.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£28.67</t>
+          <t>£28.63</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£28.67</t>
+          <t>£28.63</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£28.19</t>
+          <t>£28.16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£28.19</t>
+          <t>£28.16</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£28.19</t>
+          <t>£28.16</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1125,17 +1125,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£34.60</t>
+          <t>£34.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£34.60</t>
+          <t>£34.57</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£34.60</t>
+          <t>£34.57</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£43.05</t>
+          <t>£43.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£43.05</t>
+          <t>£43.00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£43.05</t>
+          <t>£43.00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£42.97</t>
+          <t>£42.93</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£42.97</t>
+          <t>£42.93</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£42.97</t>
+          <t>£42.93</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
